--- a/Traffic light Requirements.xlsx
+++ b/Traffic light Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79E34AC-0E20-443B-AA1A-20E5C3105F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B44241A-75EE-44CA-A861-212F982E0524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CA977AE9-5C9C-4AAA-BF1F-99241DE5163D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Functional requirements</t>
   </si>
@@ -50,24 +50,6 @@
     <t>4. When configuring the traffic light time of one road, the system shall automatically calculate the traffic light time of its crossroad.</t>
   </si>
   <si>
-    <t>1.1. The system shall have a standard mode where the lights work normally with the time configured.</t>
-  </si>
-  <si>
-    <t>1.2. The system shall have a manual mode where user can configure the time of each light using a 4x4 keyboard.</t>
-  </si>
-  <si>
-    <t>1.3. The system shall have a night mode where the yellow light blinking at 2 hz.</t>
-  </si>
-  <si>
-    <t>1.2.1 The manual mode shall allow user to switch to a specific light that will be configured the time using a button.</t>
-  </si>
-  <si>
-    <t>1.2.2. The light which is going to be configured the time shall blink to indicate that it is being configured and stop blinking when done configuring.</t>
-  </si>
-  <si>
-    <t>1.3.1. The red and green light shall be off in this mode.</t>
-  </si>
-  <si>
     <t>2. The system shall allow user to switch between modes manually by a physical button</t>
   </si>
   <si>
@@ -84,6 +66,27 @@
   </si>
   <si>
     <t>2. The system shall enter safe mode when the system resets.</t>
+  </si>
+  <si>
+    <t>1.2. The system shall have a standard mode where the lights work normally with the time configured.</t>
+  </si>
+  <si>
+    <t>1.3. The system shall have a manual mode where user can configure the time of each light.</t>
+  </si>
+  <si>
+    <t>1.4.1. The red and green light shall be off in this mode.</t>
+  </si>
+  <si>
+    <t>1.1. The system shall show information of the operating mode on an LCD display.</t>
+  </si>
+  <si>
+    <t>1.3.2. The LCD shall show the time of the light which is going to be configured.</t>
+  </si>
+  <si>
+    <t>1.3.1. The manual mode shall allow user to adjust time using 4x4 matrix keyboard.</t>
+  </si>
+  <si>
+    <t>1.4. The system shall have a safe mode where the yellow light blinks at 2 hz</t>
   </si>
 </sst>
 </file>
@@ -478,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECC89C7-4E66-4535-BCFB-96B449AAE41D}">
-  <dimension ref="A2:C24"/>
+  <dimension ref="A2:C25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:3" ht="24.6" x14ac:dyDescent="0.4">
@@ -495,72 +498,80 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>10</v>
+      <c r="A12" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A13" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>13</v>
+    <row r="22" spans="1:1" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
